--- a/tests/all.xlsx
+++ b/tests/all.xlsx
@@ -76,7 +76,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سریل نمبر</t>
+          <t xml:space="preserve">نمبر شمار</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
